--- a/GunfireDungeon_Godot/excel/BulletBase@子弹属性.xlsx
+++ b/GunfireDungeon_Godot/excel/BulletBase@子弹属性.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24765" windowHeight="14685"/>
+    <workbookView windowWidth="24765" windowHeight="12495"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="134">
   <si>
     <t>Id</t>
   </si>
@@ -121,7 +121,8 @@
   <si>
     <t>累计异常状态数据
 Burning(0):燃烧
-Poisoning(1):中毒</t>
+Poisoning(1):中毒
+Bleeding(2):出血</t>
   </si>
   <si>
     <t>造成伤害后击退值区间
@@ -273,6 +274,12 @@
   </si>
   <si>
     <t>bullet0003</t>
+  </si>
+  <si>
+    <t>"Physical":[2]</t>
+  </si>
+  <si>
+    <t>"Bleeding":5</t>
   </si>
   <si>
     <t>[320,340]</t>
@@ -1738,7 +1745,10 @@
         <v>69</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>49</v>
+        <v>70</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>71</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>61</v>
@@ -1747,13 +1757,13 @@
         <v>51</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="J6" s="1" t="s">
         <v>53</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="L6" s="2" t="s">
         <v>51</v>
@@ -1768,13 +1778,13 @@
         <v>4</v>
       </c>
       <c r="P6" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="Q6" s="1">
         <v>20</v>
       </c>
       <c r="R6" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="S6" s="3" t="s">
         <v>57</v>
@@ -1782,81 +1792,81 @@
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:19">
       <c r="A7" s="3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C7" s="1">
         <v>1</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="H7" s="1" t="s">
         <v>51</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="J7" s="1" t="s">
         <v>53</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="L7" s="2" t="s">
         <v>51</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="O7" s="2">
         <v>2</v>
       </c>
       <c r="P7" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="Q7" s="1">
         <v>16</v>
       </c>
       <c r="R7" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="S7" s="3" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="8" ht="26" customHeight="1" spans="1:19">
       <c r="A8" s="3" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C8" s="1">
         <v>1</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G8" s="1" t="s">
         <v>61</v>
@@ -1865,13 +1875,13 @@
         <v>51</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="J8" s="1" t="s">
         <v>53</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="L8" s="2" t="s">
         <v>51</v>
@@ -1892,7 +1902,7 @@
         <v>15</v>
       </c>
       <c r="R8" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="S8" s="3" t="s">
         <v>57</v>
@@ -1900,19 +1910,19 @@
     </row>
     <row r="9" customFormat="1" ht="26" customHeight="1" spans="1:19">
       <c r="A9" s="3" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C9" s="1">
         <v>1</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F9" s="1"/>
       <c r="G9" s="1" t="s">
@@ -1922,13 +1932,13 @@
         <v>51</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="J9" s="1" t="s">
         <v>53</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="L9" s="2" t="s">
         <v>51</v>
@@ -1949,7 +1959,7 @@
         <v>15</v>
       </c>
       <c r="R9" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="S9" s="3" t="s">
         <v>57</v>
@@ -1967,7 +1977,7 @@
     <row r="11" ht="29" customHeight="1" spans="1:17">
       <c r="A11" s="5"/>
       <c r="B11" s="5" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C11" s="6">
         <v>1</v>
@@ -1976,23 +1986,23 @@
         <v>48</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="F11" s="6"/>
       <c r="G11" s="6" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="H11" s="6" t="s">
         <v>51</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="J11" s="6" t="s">
         <v>53</v>
       </c>
       <c r="K11" s="6" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="L11" s="2" t="s">
         <v>51</v>
@@ -2010,37 +2020,37 @@
     <row r="12" ht="26" customHeight="1" spans="1:19">
       <c r="A12" s="3"/>
       <c r="B12" s="3" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C12" s="1">
         <v>1</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="H12" s="1" t="s">
         <v>51</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="J12" s="1" t="s">
         <v>53</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="N12" s="2" t="s">
         <v>51</v>
@@ -2049,7 +2059,7 @@
       <c r="P12" s="2"/>
       <c r="Q12" s="2"/>
       <c r="R12" s="3" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="S12" s="7" t="s">
         <v>57</v>
@@ -2058,34 +2068,34 @@
     <row r="13" ht="26" customHeight="1" spans="1:17">
       <c r="A13" s="3"/>
       <c r="B13" s="3" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C13" s="1">
         <v>1</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="H13" s="1" t="s">
         <v>51</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="J13" s="1" t="s">
         <v>53</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="M13" s="2" t="s">
         <v>51</v>
@@ -2100,16 +2110,16 @@
     <row r="16" ht="26" customHeight="1" spans="1:17">
       <c r="A16" s="3"/>
       <c r="B16" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C16" s="1">
         <v>1</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="G16" s="1" t="s">
         <v>61</v>
@@ -2118,13 +2128,13 @@
         <v>51</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="J16" s="1" t="s">
         <v>53</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="L16" s="2" t="s">
         <v>51</v>
@@ -2142,31 +2152,31 @@
     <row r="17" ht="26" customHeight="1" spans="1:17">
       <c r="A17" s="3"/>
       <c r="B17" s="3" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C17" s="1">
         <v>1</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>49</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="H17" s="1" t="s">
         <v>51</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="J17" s="1" t="s">
         <v>53</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="L17" s="2" t="s">
         <v>51</v>
@@ -2199,31 +2209,31 @@
         <v>1001</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C20" s="1">
         <v>2</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="H20" s="1" t="s">
         <v>51</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="J20" s="1" t="s">
         <v>53</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="M20" s="2" t="s">
         <v>51</v>
@@ -2236,28 +2246,28 @@
         <v>2001</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C23" s="1">
         <v>3</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="H23" s="1" t="s">
         <v>51</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="J23" s="1" t="s">
         <v>53</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
   </sheetData>

--- a/GunfireDungeon_Godot/excel/BulletBase@子弹属性.xlsx
+++ b/GunfireDungeon_Godot/excel/BulletBase@子弹属性.xlsx
@@ -276,7 +276,7 @@
     <t>bullet0003</t>
   </si>
   <si>
-    <t>"Physical":[2]</t>
+    <t>"Physical":[10]</t>
   </si>
   <si>
     <t>"Bleeding":5</t>

--- a/GunfireDungeon_Godot/excel/BulletBase@子弹属性.xlsx
+++ b/GunfireDungeon_Godot/excel/BulletBase@子弹属性.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24765" windowHeight="12495"/>
+    <workbookView windowWidth="24570" windowHeight="12240"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/GunfireDungeon_Godot/excel/BulletBase@子弹属性.xlsx
+++ b/GunfireDungeon_Godot/excel/BulletBase@子弹属性.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24570" windowHeight="12240"/>
+    <workbookView windowHeight="18800"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -108,15 +108,14 @@
   <si>
     <t>造成伤害的类型和值区间，多个key-value可以做多类型伤害
 key为伤害类型，值如下
+value为伤害值，格式为[value]或者[min,max]
 Physical(0):物理伤害
-Magic(1):魔法伤害
-Fire(2):火焰伤害
-Ice(3):冰霜伤害
-Thunder(4):雷电伤害
-Light(5):光明伤害
-Dark(6):暗影伤害
-Real(7):真实伤害
-value为伤害值，格式为[value]或者[min,max]</t>
+Fire(1):火焰伤害
+Electric(2):电击伤害
+Chemical(3):化学伤害
+Optical(4):光学伤害
+DarkMatter(5):暗物质伤害
+Explosive(6):爆破伤害</t>
   </si>
   <si>
     <t>累计异常状态数据
@@ -303,7 +302,7 @@
     <t>bullet0006</t>
   </si>
   <si>
-    <t>"Magic":[3]</t>
+    <t>"DarkMatter":[3]</t>
   </si>
   <si>
     <t>"Burning":5</t>
@@ -342,7 +341,7 @@
     <t>bullet0007</t>
   </si>
   <si>
-    <t>"Real":[2]</t>
+    <t>"Chemical":[2]</t>
   </si>
   <si>
     <t>"Poisoning":8</t>
@@ -363,7 +362,7 @@
     <t>bullet0008</t>
   </si>
   <si>
-    <t>"Real":[20]</t>
+    <t>"Chemical":[20]</t>
   </si>
   <si>
     <t>狙击枪子弹</t>
@@ -1099,13 +1098,13 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1423,18 +1422,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:S23"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
     <col min="2" max="2" width="19.375" style="1" customWidth="1"/>
     <col min="3" max="3" width="17" style="1" customWidth="1"/>
-    <col min="4" max="5" width="42.9" style="1" customWidth="1"/>
+    <col min="4" max="5" width="42.9038461538462" style="1" customWidth="1"/>
     <col min="6" max="6" width="25.375" style="1" customWidth="1"/>
-    <col min="7" max="7" width="22.725" style="1" customWidth="1"/>
-    <col min="8" max="8" width="30.4583333333333" style="1" customWidth="1"/>
+    <col min="7" max="7" width="22.7211538461538" style="1" customWidth="1"/>
+    <col min="8" max="8" width="30.4615384615385" style="1" customWidth="1"/>
     <col min="9" max="9" width="21.875" style="1" customWidth="1"/>
-    <col min="10" max="10" width="31.725" style="1" customWidth="1"/>
-    <col min="11" max="11" width="22.2583333333333" style="1" customWidth="1"/>
+    <col min="10" max="10" width="31.7211538461538" style="1" customWidth="1"/>
+    <col min="11" max="11" width="22.2596153846154" style="1" customWidth="1"/>
     <col min="12" max="12" width="17" style="1" customWidth="1"/>
     <col min="13" max="13" width="15.375" style="2" customWidth="1"/>
     <col min="14" max="17" width="19.625" style="1" customWidth="1"/>
@@ -1806,7 +1805,7 @@
       <c r="E7" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="F7" s="6" t="s">
         <v>80</v>
       </c>
       <c r="G7" s="1" t="s">
@@ -1865,7 +1864,7 @@
       <c r="E8" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="F8" s="6" t="s">
         <v>93</v>
       </c>
       <c r="G8" s="1" t="s">
@@ -1975,33 +1974,33 @@
       <c r="S10" s="3"/>
     </row>
     <row r="11" ht="29" customHeight="1" spans="1:17">
-      <c r="A11" s="5"/>
-      <c r="B11" s="5" t="s">
+      <c r="A11" s="4"/>
+      <c r="B11" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="C11" s="6">
+      <c r="C11" s="5">
         <v>1</v>
       </c>
-      <c r="D11" s="6" t="s">
+      <c r="D11" s="5" t="s">
         <v>48</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="F11" s="6"/>
-      <c r="G11" s="6" t="s">
+      <c r="F11" s="5"/>
+      <c r="G11" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="H11" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="I11" s="6" t="s">
+      <c r="H11" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="I11" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="J11" s="6" t="s">
+      <c r="J11" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="K11" s="6" t="s">
+      <c r="K11" s="5" t="s">
         <v>103</v>
       </c>
       <c r="L11" s="2" t="s">
@@ -2281,7 +2280,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -2293,7 +2292,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/GunfireDungeon_Godot/excel/BulletBase@子弹属性.xlsx
+++ b/GunfireDungeon_Godot/excel/BulletBase@子弹属性.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="18800"/>
+    <workbookView windowHeight="19180"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="133">
   <si>
     <t>Id</t>
   </si>
@@ -119,9 +119,16 @@
   </si>
   <si>
     <t>累计异常状态数据
-Burning(0):燃烧
-Poisoning(1):中毒
-Bleeding(2):出血</t>
+Bleeding（流血）：0
+Ignite（点燃）：1
+ShortCircuit（短路）：2
+Interference（干扰）：3
+ElectricShock（触电）：4
+Corrosion（腐蚀）：5
+Fragile（脆弱）：6
+Blind（致盲）：7
+Chaos（混沌）：8
+ArmorBreak（破甲）：9</t>
   </si>
   <si>
     <t>造成伤害后击退值区间
@@ -305,9 +312,6 @@
     <t>"DarkMatter":[3]</t>
   </si>
   <si>
-    <t>"Burning":5</t>
-  </si>
-  <si>
     <t>[45]</t>
   </si>
   <si>
@@ -344,7 +348,7 @@
     <t>"Chemical":[2]</t>
   </si>
   <si>
-    <t>"Poisoning":8</t>
+    <t>"Bleeding":8</t>
   </si>
   <si>
     <t>[350,380]</t>
@@ -1500,7 +1504,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" ht="183" customHeight="1" spans="1:19">
+    <row r="2" ht="204" customHeight="1" spans="1:19">
       <c r="A2" s="1" t="s">
         <v>19</v>
       </c>
@@ -1806,66 +1810,66 @@
         <v>79</v>
       </c>
       <c r="F7" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="G7" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="G7" s="1" t="s">
+      <c r="H7" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="I7" s="1" t="s">
         <v>81</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>82</v>
       </c>
       <c r="J7" s="1" t="s">
         <v>53</v>
       </c>
       <c r="K7" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="L7" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="M7" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="L7" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="M7" s="2" t="s">
+      <c r="N7" s="2" t="s">
         <v>84</v>
-      </c>
-      <c r="N7" s="2" t="s">
-        <v>85</v>
       </c>
       <c r="O7" s="2">
         <v>2</v>
       </c>
       <c r="P7" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="Q7" s="1">
         <v>16</v>
       </c>
       <c r="R7" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="S7" s="3" t="s">
         <v>87</v>
-      </c>
-      <c r="S7" s="3" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="8" ht="26" customHeight="1" spans="1:19">
       <c r="A8" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>89</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>90</v>
       </c>
       <c r="C8" s="1">
         <v>1</v>
       </c>
       <c r="D8" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="E8" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="E8" s="1" t="s">
+      <c r="F8" s="6" t="s">
         <v>92</v>
-      </c>
-      <c r="F8" s="6" t="s">
-        <v>93</v>
       </c>
       <c r="G8" s="1" t="s">
         <v>61</v>
@@ -1874,13 +1878,13 @@
         <v>51</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="J8" s="1" t="s">
         <v>53</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L8" s="2" t="s">
         <v>51</v>
@@ -1901,7 +1905,7 @@
         <v>15</v>
       </c>
       <c r="R8" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="S8" s="3" t="s">
         <v>57</v>
@@ -1909,19 +1913,19 @@
     </row>
     <row r="9" customFormat="1" ht="26" customHeight="1" spans="1:19">
       <c r="A9" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>96</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>97</v>
       </c>
       <c r="C9" s="1">
         <v>1</v>
       </c>
       <c r="D9" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="E9" s="1" t="s">
         <v>98</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>99</v>
       </c>
       <c r="F9" s="1"/>
       <c r="G9" s="1" t="s">
@@ -1931,13 +1935,13 @@
         <v>51</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="J9" s="1" t="s">
         <v>53</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L9" s="2" t="s">
         <v>51</v>
@@ -1958,7 +1962,7 @@
         <v>15</v>
       </c>
       <c r="R9" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="S9" s="3" t="s">
         <v>57</v>
@@ -1976,7 +1980,7 @@
     <row r="11" ht="29" customHeight="1" spans="1:17">
       <c r="A11" s="4"/>
       <c r="B11" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C11" s="5">
         <v>1</v>
@@ -1985,23 +1989,23 @@
         <v>48</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F11" s="5"/>
       <c r="G11" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="H11" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="I11" s="5" t="s">
         <v>102</v>
-      </c>
-      <c r="H11" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="I11" s="5" t="s">
-        <v>103</v>
       </c>
       <c r="J11" s="5" t="s">
         <v>53</v>
       </c>
       <c r="K11" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="L11" s="2" t="s">
         <v>51</v>
@@ -2019,37 +2023,37 @@
     <row r="12" ht="26" customHeight="1" spans="1:19">
       <c r="A12" s="3"/>
       <c r="B12" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C12" s="1">
         <v>1</v>
       </c>
       <c r="D12" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="E12" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="E12" s="1" t="s">
+      <c r="G12" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="G12" s="1" t="s">
+      <c r="H12" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="I12" s="1" t="s">
         <v>107</v>
-      </c>
-      <c r="H12" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="I12" s="1" t="s">
-        <v>108</v>
       </c>
       <c r="J12" s="1" t="s">
         <v>53</v>
       </c>
       <c r="K12" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="L12" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="L12" s="1" t="s">
+      <c r="M12" s="2" t="s">
         <v>110</v>
-      </c>
-      <c r="M12" s="2" t="s">
-        <v>111</v>
       </c>
       <c r="N12" s="2" t="s">
         <v>51</v>
@@ -2058,7 +2062,7 @@
       <c r="P12" s="2"/>
       <c r="Q12" s="2"/>
       <c r="R12" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="S12" s="7" t="s">
         <v>57</v>
@@ -2067,34 +2071,34 @@
     <row r="13" ht="26" customHeight="1" spans="1:17">
       <c r="A13" s="3"/>
       <c r="B13" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C13" s="1">
         <v>1</v>
       </c>
       <c r="D13" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="E13" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="E13" s="1" t="s">
+      <c r="G13" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="G13" s="1" t="s">
+      <c r="H13" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="I13" s="1" t="s">
         <v>116</v>
-      </c>
-      <c r="H13" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="I13" s="1" t="s">
-        <v>117</v>
       </c>
       <c r="J13" s="1" t="s">
         <v>53</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="M13" s="2" t="s">
         <v>51</v>
@@ -2109,16 +2113,16 @@
     <row r="16" ht="26" customHeight="1" spans="1:17">
       <c r="A16" s="3"/>
       <c r="B16" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C16" s="1">
         <v>1</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="G16" s="1" t="s">
         <v>61</v>
@@ -2127,13 +2131,13 @@
         <v>51</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="J16" s="1" t="s">
         <v>53</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L16" s="2" t="s">
         <v>51</v>
@@ -2151,31 +2155,31 @@
     <row r="17" ht="26" customHeight="1" spans="1:17">
       <c r="A17" s="3"/>
       <c r="B17" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C17" s="1">
         <v>1</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>49</v>
       </c>
       <c r="G17" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="I17" s="1" t="s">
         <v>123</v>
-      </c>
-      <c r="H17" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="I17" s="1" t="s">
-        <v>124</v>
       </c>
       <c r="J17" s="1" t="s">
         <v>53</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="L17" s="2" t="s">
         <v>51</v>
@@ -2208,31 +2212,31 @@
         <v>1001</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C20" s="1">
         <v>2</v>
       </c>
       <c r="D20" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="E20" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="E20" s="1" t="s">
+      <c r="G20" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="G20" s="1" t="s">
+      <c r="H20" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="I20" s="1" t="s">
         <v>129</v>
-      </c>
-      <c r="H20" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="I20" s="1" t="s">
-        <v>130</v>
       </c>
       <c r="J20" s="1" t="s">
         <v>53</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="M20" s="2" t="s">
         <v>51</v>
@@ -2245,28 +2249,28 @@
         <v>2001</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C23" s="1">
         <v>3</v>
       </c>
       <c r="E23" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="I23" s="1" t="s">
         <v>132</v>
-      </c>
-      <c r="G23" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="H23" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="I23" s="1" t="s">
-        <v>133</v>
       </c>
       <c r="J23" s="1" t="s">
         <v>53</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
   </sheetData>

--- a/GunfireDungeon_Godot/excel/BulletBase@子弹属性.xlsx
+++ b/GunfireDungeon_Godot/excel/BulletBase@子弹属性.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="139">
   <si>
     <t>Id</t>
   </si>
@@ -43,10 +43,19 @@
     <t>Prefab</t>
   </si>
   <si>
-    <t>Harm</t>
+    <t>Damage</t>
   </si>
   <si>
     <t>AbnormalState</t>
+  </si>
+  <si>
+    <t>CritRate</t>
+  </si>
+  <si>
+    <t>CritBonus</t>
+  </si>
+  <si>
+    <t>CritArmorPenetration</t>
   </si>
   <si>
     <t>RepelRange</t>
@@ -131,6 +140,15 @@
 ArmorBreak（破甲）：9</t>
   </si>
   <si>
+    <t>暴击率（0-1）</t>
+  </si>
+  <si>
+    <t>暴击伤害修正（例如0.25表示+25%）</t>
+  </si>
+  <si>
+    <t>暴击穿透装甲比例（例如0.25）</t>
+  </si>
+  <si>
     <t>造成伤害后击退值区间
 如果发射子弹,则按每发子弹算击退
 格式为[value]或者[min,max]</t>
@@ -198,13 +216,13 @@
     <t>{AbnormalStateType:int}*</t>
   </si>
   <si>
+    <t>float</t>
+  </si>
+  <si>
     <t>[float]</t>
   </si>
   <si>
     <t>[int]</t>
-  </si>
-  <si>
-    <t>float</t>
   </si>
   <si>
     <t>$Sound</t>
@@ -1425,27 +1443,27 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:S23"/>
+  <dimension ref="A1:V23"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
     <col min="2" max="2" width="19.375" style="1" customWidth="1"/>
     <col min="3" max="3" width="17" style="1" customWidth="1"/>
     <col min="4" max="5" width="42.9038461538462" style="1" customWidth="1"/>
-    <col min="6" max="6" width="25.375" style="1" customWidth="1"/>
-    <col min="7" max="7" width="22.7211538461538" style="1" customWidth="1"/>
-    <col min="8" max="8" width="30.4615384615385" style="1" customWidth="1"/>
-    <col min="9" max="9" width="21.875" style="1" customWidth="1"/>
-    <col min="10" max="10" width="31.7211538461538" style="1" customWidth="1"/>
-    <col min="11" max="11" width="22.2596153846154" style="1" customWidth="1"/>
-    <col min="12" max="12" width="17" style="1" customWidth="1"/>
-    <col min="13" max="13" width="15.375" style="2" customWidth="1"/>
-    <col min="14" max="17" width="19.625" style="1" customWidth="1"/>
-    <col min="18" max="18" width="14.875" customWidth="1"/>
-    <col min="19" max="19" width="50.375" customWidth="1"/>
+    <col min="6" max="9" width="25.375" style="1" customWidth="1"/>
+    <col min="10" max="10" width="22.7211538461538" style="1" customWidth="1"/>
+    <col min="11" max="11" width="30.4615384615385" style="1" customWidth="1"/>
+    <col min="12" max="12" width="21.875" style="1" customWidth="1"/>
+    <col min="13" max="13" width="31.7211538461538" style="1" customWidth="1"/>
+    <col min="14" max="14" width="22.2596153846154" style="1" customWidth="1"/>
+    <col min="15" max="15" width="17" style="1" customWidth="1"/>
+    <col min="16" max="16" width="15.375" style="2" customWidth="1"/>
+    <col min="17" max="20" width="19.625" style="1" customWidth="1"/>
+    <col min="21" max="21" width="14.875" customWidth="1"/>
+    <col min="22" max="22" width="50.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="33" customHeight="1" spans="1:19">
+    <row r="1" ht="33" customHeight="1" spans="1:22">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1482,7 +1500,7 @@
       <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
       <c r="N1" s="1" t="s">
@@ -1491,7 +1509,7 @@
       <c r="O1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" s="2" t="s">
         <v>15</v>
       </c>
       <c r="Q1" s="1" t="s">
@@ -1503,774 +1521,858 @@
       <c r="S1" s="1" t="s">
         <v>18</v>
       </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>21</v>
+      </c>
     </row>
-    <row r="2" ht="204" customHeight="1" spans="1:19">
+    <row r="2" ht="204" customHeight="1" spans="1:22">
       <c r="A2" s="1" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="M2" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>34</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="P2" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="Q2" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="S2" s="1" t="s">
-        <v>37</v>
+        <v>40</v>
+      </c>
+      <c r="T2" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="U2" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="V2" s="1" t="s">
+        <v>43</v>
       </c>
     </row>
-    <row r="3" ht="27" customHeight="1" spans="1:19">
+    <row r="3" ht="27" customHeight="1" spans="1:22">
       <c r="A3" s="1" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="M3" s="2" t="s">
-        <v>43</v>
+        <v>49</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="O3" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="P3" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q3" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="R3" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="S3" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="T3" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="U3" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="V3" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="P3" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q3" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="R3" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="S3" s="1" t="s">
-        <v>38</v>
-      </c>
     </row>
-    <row r="4" ht="28" customHeight="1" spans="1:19">
+    <row r="4" ht="28" customHeight="1" spans="1:22">
       <c r="A4" s="3" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="C4" s="1">
         <v>1</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>52</v>
+        <v>55</v>
+      </c>
+      <c r="G4" s="1">
+        <v>0.3</v>
+      </c>
+      <c r="H4" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="I4" s="1">
+        <v>0.4</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="L4" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="M4" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="N4" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="O4" s="2">
+        <v>57</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="M4" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="N4" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="O4" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="P4" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q4" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="R4" s="2">
         <v>2</v>
       </c>
-      <c r="P4" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="Q4" s="1">
+      <c r="S4" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="T4" s="1">
         <v>10</v>
       </c>
-      <c r="R4" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="S4" s="3" t="s">
-        <v>57</v>
+      <c r="U4" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="V4" s="3" t="s">
+        <v>63</v>
       </c>
     </row>
-    <row r="5" ht="26" customHeight="1" spans="1:19">
+    <row r="5" ht="26" customHeight="1" spans="1:22">
       <c r="A5" s="3" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="C5" s="1">
         <v>1</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="I5" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="G5" s="1">
+        <v>0.3</v>
+      </c>
+      <c r="H5" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="I5" s="1">
+        <v>0.4</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="M5" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="N5" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="O5" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="P5" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q5" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="R5" s="2">
+        <v>2</v>
+      </c>
+      <c r="S5" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="T5" s="1">
+        <v>15</v>
+      </c>
+      <c r="U5" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="V5" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="J5" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="K5" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="L5" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="M5" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="N5" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="O5" s="2">
-        <v>2</v>
-      </c>
-      <c r="P5" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="Q5" s="1">
-        <v>15</v>
-      </c>
-      <c r="R5" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="S5" s="3" t="s">
-        <v>57</v>
-      </c>
     </row>
-    <row r="6" ht="29" customHeight="1" spans="1:19">
+    <row r="6" ht="29" customHeight="1" spans="1:22">
       <c r="A6" s="3" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="C6" s="1">
         <v>1</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>72</v>
+        <v>77</v>
+      </c>
+      <c r="G6" s="1">
+        <v>0.3</v>
+      </c>
+      <c r="H6" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="I6" s="1">
+        <v>0.4</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="L6" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="M6" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="N6" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="O6" s="2">
+        <v>57</v>
+      </c>
+      <c r="L6" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="M6" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="N6" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="O6" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="P6" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q6" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="R6" s="2">
         <v>4</v>
       </c>
-      <c r="P6" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="Q6" s="1">
+      <c r="S6" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="T6" s="1">
         <v>20</v>
       </c>
-      <c r="R6" t="s">
-        <v>75</v>
-      </c>
-      <c r="S6" s="3" t="s">
-        <v>57</v>
+      <c r="U6" t="s">
+        <v>81</v>
+      </c>
+      <c r="V6" s="3" t="s">
+        <v>63</v>
       </c>
     </row>
-    <row r="7" ht="28" customHeight="1" spans="1:19">
+    <row r="7" ht="28" customHeight="1" spans="1:22">
       <c r="A7" s="3" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="C7" s="1">
         <v>1</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>81</v>
+        <v>77</v>
+      </c>
+      <c r="G7" s="1">
+        <v>0.3</v>
+      </c>
+      <c r="H7" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="I7" s="1">
+        <v>0.4</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>53</v>
+        <v>86</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="L7" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="M7" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="N7" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="O7" s="2">
+        <v>57</v>
+      </c>
+      <c r="L7" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="M7" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="N7" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="O7" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="P7" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q7" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="R7" s="2">
         <v>2</v>
       </c>
-      <c r="P7" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="Q7" s="1">
+      <c r="S7" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="T7" s="1">
         <v>16</v>
       </c>
-      <c r="R7" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="S7" s="3" t="s">
-        <v>87</v>
+      <c r="U7" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="V7" s="3" t="s">
+        <v>93</v>
       </c>
     </row>
-    <row r="8" ht="26" customHeight="1" spans="1:19">
+    <row r="8" ht="26" customHeight="1" spans="1:22">
       <c r="A8" s="3" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="C8" s="1">
         <v>1</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="F8" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="G8" s="1">
+        <v>0.3</v>
+      </c>
+      <c r="H8" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="I8" s="1">
+        <v>0.4</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="L8" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="M8" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="N8" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="O8" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="P8" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q8" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="R8" s="2">
+        <v>2</v>
+      </c>
+      <c r="S8" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="T8" s="1">
+        <v>15</v>
+      </c>
+      <c r="U8" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="G8" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="I8" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="J8" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="K8" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="L8" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="M8" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="N8" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="O8" s="2">
-        <v>2</v>
-      </c>
-      <c r="P8" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="Q8" s="1">
-        <v>15</v>
-      </c>
-      <c r="R8" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="S8" s="3" t="s">
-        <v>57</v>
+      <c r="V8" s="3" t="s">
+        <v>63</v>
       </c>
     </row>
-    <row r="9" customFormat="1" ht="26" customHeight="1" spans="1:19">
+    <row r="9" customFormat="1" ht="26" customHeight="1" spans="1:22">
       <c r="A9" s="3" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="C9" s="1">
         <v>1</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="F9" s="1"/>
-      <c r="G9" s="1" t="s">
+      <c r="G9" s="1">
+        <v>0.3</v>
+      </c>
+      <c r="H9" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="I9" s="1">
+        <v>0.4</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="L9" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="M9" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="N9" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="O9" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="P9" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q9" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="R9" s="2">
+        <v>2</v>
+      </c>
+      <c r="S9" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="H9" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="I9" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="J9" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="K9" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="L9" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="M9" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="N9" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="O9" s="2">
-        <v>2</v>
-      </c>
-      <c r="P9" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="Q9" s="1">
+      <c r="T9" s="1">
         <v>15</v>
       </c>
-      <c r="R9" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="S9" s="3" t="s">
-        <v>57</v>
+      <c r="U9" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="V9" s="3" t="s">
+        <v>63</v>
       </c>
     </row>
-    <row r="10" ht="29" customHeight="1" spans="1:19">
+    <row r="10" ht="29" customHeight="1" spans="1:22">
       <c r="A10" s="3"/>
-      <c r="L10" s="2"/>
-      <c r="N10" s="2"/>
       <c r="O10" s="2"/>
-      <c r="P10" s="2"/>
       <c r="Q10" s="2"/>
-      <c r="S10" s="3"/>
+      <c r="R10" s="2"/>
+      <c r="S10" s="2"/>
+      <c r="T10" s="2"/>
+      <c r="V10" s="3"/>
     </row>
-    <row r="11" ht="29" customHeight="1" spans="1:17">
+    <row r="11" ht="29" customHeight="1" spans="1:20">
       <c r="A11" s="4"/>
       <c r="B11" s="4" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="C11" s="5">
         <v>1</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="F11" s="5"/>
-      <c r="G11" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="H11" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="I11" s="5" t="s">
-        <v>102</v>
-      </c>
+      <c r="G11" s="5"/>
+      <c r="H11" s="5"/>
+      <c r="I11" s="5"/>
       <c r="J11" s="5" t="s">
-        <v>53</v>
+        <v>107</v>
       </c>
       <c r="K11" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="L11" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="M11" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="N11" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="O11" s="2"/>
-      <c r="P11" s="2"/>
-      <c r="Q11" s="2"/>
+        <v>57</v>
+      </c>
+      <c r="L11" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="M11" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="N11" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="O11" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="P11" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q11" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="R11" s="2"/>
+      <c r="S11" s="2"/>
+      <c r="T11" s="2"/>
     </row>
-    <row r="12" ht="26" customHeight="1" spans="1:19">
+    <row r="12" ht="26" customHeight="1" spans="1:22">
       <c r="A12" s="3"/>
       <c r="B12" s="3" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="C12" s="1">
         <v>1</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="G12" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="H12" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="I12" s="1" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>53</v>
+        <v>112</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>108</v>
+        <v>57</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="M12" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="N12" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="O12" s="2"/>
-      <c r="P12" s="2"/>
-      <c r="Q12" s="2"/>
-      <c r="R12" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="S12" s="7" t="s">
-        <v>57</v>
+        <v>113</v>
+      </c>
+      <c r="M12" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="N12" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="O12" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="P12" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="Q12" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="R12" s="2"/>
+      <c r="S12" s="2"/>
+      <c r="T12" s="2"/>
+      <c r="U12" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="V12" s="7" t="s">
+        <v>63</v>
       </c>
     </row>
-    <row r="13" ht="26" customHeight="1" spans="1:17">
+    <row r="13" ht="26" customHeight="1" spans="1:20">
       <c r="A13" s="3"/>
       <c r="B13" s="3" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="C13" s="1">
         <v>1</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="E13" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="J13" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="K13" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="L13" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="M13" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="N13" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="G13" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="H13" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="I13" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="J13" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="K13" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="L13" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="M13" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="N13" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="O13" s="2"/>
-      <c r="P13" s="2"/>
-      <c r="Q13" s="2"/>
+      <c r="O13" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="P13" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q13" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="R13" s="2"/>
+      <c r="S13" s="2"/>
+      <c r="T13" s="2"/>
     </row>
-    <row r="16" ht="26" customHeight="1" spans="1:17">
+    <row r="16" ht="26" customHeight="1" spans="1:20">
       <c r="A16" s="3"/>
       <c r="B16" s="3" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="C16" s="1">
         <v>1</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="G16" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="H16" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="I16" s="1" t="s">
-        <v>93</v>
+        <v>125</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="L16" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="M16" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="N16" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="O16" s="2"/>
-      <c r="P16" s="2"/>
-      <c r="Q16" s="2"/>
+        <v>57</v>
+      </c>
+      <c r="L16" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="M16" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="N16" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="O16" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="P16" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q16" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="R16" s="2"/>
+      <c r="S16" s="2"/>
+      <c r="T16" s="2"/>
     </row>
-    <row r="17" ht="26" customHeight="1" spans="1:17">
+    <row r="17" ht="26" customHeight="1" spans="1:20">
       <c r="A17" s="3"/>
       <c r="B17" s="3" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="C17" s="1">
         <v>1</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="G17" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="H17" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="I17" s="1" t="s">
-        <v>123</v>
+        <v>55</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>53</v>
+        <v>128</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="L17" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="M17" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="N17" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="O17" s="2"/>
-      <c r="P17" s="2"/>
-      <c r="Q17" s="2"/>
+        <v>57</v>
+      </c>
+      <c r="L17" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="M17" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="N17" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="O17" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="P17" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q17" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="R17" s="2"/>
+      <c r="S17" s="2"/>
+      <c r="T17" s="2"/>
     </row>
-    <row r="18" ht="26" customHeight="1" spans="1:17">
+    <row r="18" ht="26" customHeight="1" spans="1:20">
       <c r="A18" s="3"/>
       <c r="B18" s="3"/>
-      <c r="L18" s="2"/>
-      <c r="N18" s="2"/>
       <c r="O18" s="2"/>
-      <c r="P18" s="2"/>
       <c r="Q18" s="2"/>
+      <c r="R18" s="2"/>
+      <c r="S18" s="2"/>
+      <c r="T18" s="2"/>
     </row>
     <row r="19" ht="26" customHeight="1" spans="1:2">
       <c r="A19" s="3"/>
       <c r="B19" s="3"/>
     </row>
-    <row r="20" ht="25" customHeight="1" spans="1:13">
+    <row r="20" ht="25" customHeight="1" spans="1:16">
       <c r="A20" s="1">
         <v>1001</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="C20" s="1">
         <v>2</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="G20" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="H20" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="I20" s="1" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>53</v>
+        <v>134</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="M20" s="2" t="s">
-        <v>51</v>
+        <v>57</v>
+      </c>
+      <c r="L20" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="M20" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="N20" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="P20" s="2" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="21" ht="25" customHeight="1"/>
     <row r="22" ht="25" customHeight="1"/>
-    <row r="23" ht="20" customHeight="1" spans="1:11">
+    <row r="23" ht="20" customHeight="1" spans="1:14">
       <c r="A23" s="1">
         <v>2001</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="C23" s="1">
         <v>3</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="G23" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="H23" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="I23" s="1" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>53</v>
+        <v>115</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>128</v>
+        <v>57</v>
+      </c>
+      <c r="L23" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="M23" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="N23" s="1" t="s">
+        <v>134</v>
       </c>
     </row>
   </sheetData>
